--- a/EstablecimientoSalud/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/EstablecimientoSalud/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,12 +741,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,27 +761,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.12254973</t>
+          <t>-9.057738</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-78.52786414</t>
+          <t>-78.587071</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CLINICA MEDICO OCUPACIONAL CARRION S.A.C.</t>
+          <t>"CENTRO DE SALUD MENTAL COMUNITARIO DOS DE JUNIO"</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>URBANIZACION LOS CIPRESES MZ R LT 14 / AV. ARGENTINA S/N A 250 METROS DE LA PLAZA MAYOR DE NUEVO CHIMBOTE MANZANA R LOTE 14 URBANIZACION LOS CIPRESES DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS PUEBLO JOVEN 2 DE JUNIO L 02 A DOS CUADRAS DEL VIVERO FORESTAL DE CHIMBOTE CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,22 +828,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-9.057738</t>
+          <t>-9.08843009</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.587071</t>
+          <t>-78.57040973</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>"CENTRO DE SALUD MENTAL COMUNITARIO DOS DE JUNIO"</t>
+          <t>CENTRO DE SALUD MIRAFLORES ALTO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OTROS PUEBLO JOVEN 2 DE JUNIO L 02 A DOS CUADRAS DEL VIVERO FORESTAL DE CHIMBOTE CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS PP.JJ. MIRAFLORES ALTO MZ. 23 - 1 PP.JJ. MIRAFLORES ALTO MZ. 23 - 1 CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-9.08843009</t>
+          <t>-8.94403612</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.57040973</t>
+          <t>-78.5170778</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MIRAFLORES ALTO</t>
+          <t>PUESTO DE SALUD 14 INCAS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OTROS PP.JJ. MIRAFLORES ALTO MZ. 23 - 1 PP.JJ. MIRAFLORES ALTO MZ. 23 - 1 CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS 14 INCAS CASCAJAL IZQUIERDO S/NN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,12 +927,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -947,27 +947,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>CACERES DEL PERU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.94403612</t>
+          <t>-8.87063242</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-78.5170778</t>
+          <t>-78.15358285</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD 14 INCAS</t>
+          <t>PUESTO DE SALUD SANTA ROSA DE PAQUIRCA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OTROS 14 INCAS CASCAJAL IZQUIERDO S/NN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS SANTA ROSA DE PAQUIRCA S/N - CENTRO POBLADO SANTA ROSA DE PAQUIRCAN° S/N DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -989,12 +989,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CACERES DEL PERU</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.87063242</t>
+          <t>-9.147672</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-78.15358285</t>
+          <t>-78.507196</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SANTA ROSA DE PAQUIRCA</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO NUEVO PUERTO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OTROS SANTA ROSA DE PAQUIRCA S/N - CENTRO POBLADO SANTA ROSA DE PAQUIRCAN° S/N DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS ASENTAMIENTO HUMANO VILLA LAS PALMAS C O2 A ESPALDAS DEL COLEGIO LAS PALMAS NUEVO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-9.1309096</t>
+          <t>-8.98607928</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-78.5226312</t>
+          <t>-78.6153025</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CLINICA SSOSMA SAC</t>
+          <t>CENTRO DE SALUD SANTA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AVENIDA AV. LOS ALAMOS MZ - J - LT - 01 - NUEVO CHIMBOTE DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>Jr. JR. RIO SANTA Nº 510 MZ. A LT 02 JR. RIO SANTA Nº 510 MZ. A LT 02 SANTA SANTA ANCASH</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1113,12 +1113,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>31454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1133,27 +1133,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.147672</t>
+          <t>-9.05707165</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-78.507196</t>
+          <t>-78.58185257</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO NUEVO PUERTO</t>
+          <t>CENTRO DE SALUD LA ESPERANZA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OTROS ASENTAMIENTO HUMANO VILLA LAS PALMAS C O2 A ESPALDAS DEL COLEGIO LAS PALMAS NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>Jr. RAMON CASTILLA H 01 A UNA CUADRA DEL CEMENTAERIO DIVINO MAESTRO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1195,32 +1195,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.98607928</t>
+          <t>-9.09278314</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-78.6153025</t>
+          <t>-78.56165175</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SANTA</t>
+          <t>PUESTO DE SALUD SAN JUAN</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jr. JR. RIO SANTA Nº 510 MZ. A LT 02 JR. RIO SANTA Nº 510 MZ. A LT 02 SANTA SANTA ANCASH</t>
+          <t>OTROS JOSE CARLOS MARIATEGUI S/NN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31454</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.05707165</t>
+          <t>-9.1189991</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-78.58185257</t>
+          <t>-78.54523354</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD LA ESPERANZA</t>
+          <t>PUESTO DE SALUD VILLA MARIA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jr. RAMON CASTILLA H 01 A UNA CUADRA DEL CEMENTAERIO DIVINO MAESTRO CHIMBOTE SANTA ANCASH</t>
+          <t>AVENIDA AV. 28 DE JULIO MZ Z-17A VILLA MARIA AV. 28 DE JULIO MZ Z-17A VILLA MARIA NUEVO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,12 +1299,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1319,32 +1319,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>MORO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.09278314</t>
+          <t>-9.10062144</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-78.56165175</t>
+          <t>-78.1818235</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SAN JUAN</t>
+          <t>PUESTO DE SALUD CAPTUY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OTROS JOSE CARLOS MARIATEGUI S/NN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS CAPTUY BAJO DISTRITO MORO PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,12 +1361,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1381,32 +1381,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-9.1189991</t>
+          <t>-9.02166397</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-78.54523354</t>
+          <t>-78.6140252</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD VILLA MARIA</t>
+          <t>CENTRO DE SALUD COISHCO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AVENIDA AV. 28 DE JULIO MZ Z-17A VILLA MARIA AV. 28 DE JULIO MZ Z-17A VILLA MARIA NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS PANAMERICANA ANTIGUA Nº 599 MZ W1 LTE. 16 PANAMERICANA ANTIGUA Nº 599 MZ W1 LTE. 16 COISHCO SANTA ANCASH</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1443,32 +1443,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MORO</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-9.10062144</t>
+          <t>-9.0746192</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-78.1818235</t>
+          <t>-78.595333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CAPTUY</t>
+          <t>POLICLINICO PNP CHIMBOTE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OTROS CAPTUY BAJO DISTRITO MORO PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA PARDO 292 NUMERO 292 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1485,12 +1485,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>36302</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1505,27 +1505,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>COISHCO</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-9.02166397</t>
+          <t>-8.993822</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-78.6140252</t>
+          <t>-78.615623</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD COISHCO</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "SANTA"</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OTROS PANAMERICANA ANTIGUA Nº 599 MZ W1 LTE. 16 PANAMERICANA ANTIGUA Nº 599 MZ W1 LTE. 16 COISHCO SANTA ANCASH</t>
+          <t>PROLONGACION CIRO ALEGRIA MANZANA WÂ´ LOTE 1 DISTRITO SANTA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,27 +1572,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.0746192</t>
+          <t>-9.05027294</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-78.595333</t>
+          <t>-78.58886325</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>POLICLINICO PNP CHIMBOTE</t>
+          <t>PUESTO DE SALUD SAN PEDRO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AVENIDA PARDO 292 NUMERO 292 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>Jr. JR.LOS ANGELES MZ-L1 -LT -1 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,27 +1634,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-9.1237737</t>
+          <t>-9.124726</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-78.4969311</t>
+          <t>-78.5233296</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>POLICLINICO JIREH</t>
+          <t>HOSPITAL I CONO SUR</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AVENIDA SAN ANTONIO MANZANA A LOTE 04,05 y 21 DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AV.ANCHOVETA S/NN° S/N DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1691,32 +1691,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>SAMANCO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.993822</t>
+          <t>-9.31965602</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-78.615623</t>
+          <t>-78.47588709</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "SANTA"</t>
+          <t>PUESTO DE SALUD LOS CHIMUS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PROLONGACION CIRO ALEGRIA MANZANA WÂ´ LOTE 1 DISTRITO SANTA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AV. PESCADORES S/N CENTRO POBLADO CALETA - LOS CHIMUSN° S/N DISTRITO SAMANCO PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1733,12 +1733,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1753,27 +1753,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-9.05027294</t>
+          <t>-9.11697211</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-78.58886325</t>
+          <t>-78.5049083</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SAN PEDRO</t>
+          <t>PUESTO DE SALUD NICOLAS DE GARATEA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Jr. JR.LOS ANGELES MZ-L1 -LT -1 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS NICOLAS DE GARATEA MZ 90 LTE 05 NICOLAS DE GARATEA MZ 90 LTE 05 NUEVO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1815,32 +1815,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-9.124726</t>
+          <t>-9.05013822</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-78.5233296</t>
+          <t>-78.5744781</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HOSPITAL I CONO SUR</t>
+          <t>PUESTO DE SALUD LA UNION</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AVENIDA AV.ANCHOVETA S/NN° S/N DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>Jr. JR. MANCO CAPAC S/N MZA 1 LTE. 10A S/N JR. MANCO CAPAC S/N MZA 1 LTE. 10A CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1857,12 +1857,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1877,32 +1877,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SAMANCO</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-9.31965602</t>
+          <t>-9.10852269</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-78.47588709</t>
+          <t>-78.53781565</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD LOS CHIMUS</t>
+          <t>PUESTO DE SALUD SATELITE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AVENIDA AV. PESCADORES S/N CENTRO POBLADO CALETA - LOS CHIMUSN° S/N DISTRITO SAMANCO PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>CALLE CALLE MEXICO MZ N LT 4 CALLE MEXICO MZ N LT 4 NUEVO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1939,27 +1939,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-9.11697211</t>
+          <t>-9.05971975</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-78.5049083</t>
+          <t>-78.57915935</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD NICOLAS DE GARATEA</t>
+          <t>PUESTO DE SALUD TUPAC AMARU</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OTROS NICOLAS DE GARATEA MZ 90 LTE 05 NICOLAS DE GARATEA MZ 90 LTE 05 NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS URB. EL CARMEN MZ 13- LOTE 8-A DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2001,27 +2001,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.05013822</t>
+          <t>-9.11610303</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-78.5744781</t>
+          <t>-78.53955184</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD LA UNION</t>
+          <t>PUESTO DE SALUD 3 DE OCTUBRE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Jr. JR. MANCO CAPAC S/N MZA 1 LTE. 10A S/N JR. MANCO CAPAC S/N MZA 1 LTE. 10A CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS MZR-LOTE3 A.H. 03 DE OCTUBRE MZR-LOTE3 A.H. 03 DE OCTUBRE NUEVO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2063,32 +2063,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>SAMANCO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-9.10852269</t>
+          <t>-9.25819043</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-78.53781565</t>
+          <t>-78.43538633</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SATELITE</t>
+          <t>PUESTO DE SALUD HUAMBACHO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CALLE CALLE MEXICO MZ N LT 4 CALLE MEXICO MZ N LT 4 NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS HUAMBACHO EL ARENAL HUAMBACHO EL ARENAL SAMANCO SANTA ANCASH</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2105,12 +2105,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2125,32 +2125,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>MACATE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-9.13579</t>
+          <t>-8.76132536</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-78.52038</t>
+          <t>-78.09455399</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CENTRO MADICO MEDIC VIP</t>
+          <t>PUESTO DE SALUD HUANROC</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>URBANIZACION BRUCES MANZANA J LOTE II DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS TUCUPARA - BELLAVISTA - HUARAC DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34521</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2187,32 +2187,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-9.11910248</t>
+          <t>-8.89325253</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-78.5244577</t>
+          <t>-78.56666266</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SANTA FE</t>
+          <t>PUESTO DE SALUD RINCONADA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AVENIDA BRASIL MANZANA A LOTE 3 URBANIZACION LOS ALAMOS DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AV.VICTOR RAUL HAYA DE LA TORRE S/NN° S/N DISTRITO SANTA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2229,12 +2229,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2249,32 +2249,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-9.07171004</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-78.52</t>
+          <t>-78.58178337</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO RIVERALAB</t>
+          <t>PUESTO DE SALUD MAGDALENA NUEVA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OTROS URB. SAN RAFAEL MZ C 5 LOTE 9 DISTRITO NUEVO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AVENIDA ATAHUALPA CUADRA 3 S/N. S/N AVENIDA ATAHUALPA CUADRA 3 S/N. CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2291,7 +2291,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2316,27 +2316,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-9.05971975</t>
+          <t>-8.97323873</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-78.57915935</t>
+          <t>-78.49818145</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD TUPAC AMARU</t>
+          <t>PUESTO DE SALUD CHACHAPOYAS</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OTROS URB. EL CARMEN MZ 13- LOTE 8-A DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AV. SANTA ROSA MZ D LTE 2 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2353,7 +2353,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2378,32 +2378,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-9.11610303</t>
+          <t>-9.1323422</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-78.53955184</t>
+          <t>-78.51919552</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD 3 DE OCTUBRE</t>
+          <t>CENTRO DE SALUD YUGOSLAVIA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>OTROS MZR-LOTE3 A.H. 03 DE OCTUBRE MZR-LOTE3 A.H. 03 DE OCTUBRE NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>AVENIDA AV. SAUCES S/N NUEVO CHIMBOTE S/N AV. SAUCES S/N NUEVO CHIMBOTE NUEVO CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2415,12 +2415,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2435,27 +2435,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SAMANCO</t>
+          <t>CACERES DEL PERU</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-9.25819043</t>
+          <t>-8.93579691</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-78.43538633</t>
+          <t>-78.14516733</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD HUAMBACHO</t>
+          <t>PUESTO DE SALUD LAMPANIN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OTROS HUAMBACHO EL ARENAL HUAMBACHO EL ARENAL SAMANCO SANTA ANCASH</t>
+          <t>OTROS CASERIO LAMPANIN DISTRITO CACERES DEL PERU PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2477,12 +2477,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2497,32 +2497,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MACATE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-8.76132536</t>
+          <t>-9.074195</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-78.09455399</t>
+          <t>-78.56754</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD HUANROC</t>
+          <t>PUESTO DE SALUD SANTA ANA COSTA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OTROS TUCUPARA - BELLAVISTA - HUARAC DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS ASENTAMIENTO HUMANO SAN MIGUEL MANZANA L LOTE 2 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2559,32 +2559,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>NEPEÑA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-8.89325253</t>
+          <t>-9.14530627</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-78.56666266</t>
+          <t>-78.27668369</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD RINCONADA</t>
+          <t>CENTRO DE SALUD SAN JACINTO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AVENIDA AV.VICTOR RAUL HAYA DE LA TORRE S/NN° S/N DISTRITO SANTA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AV. SOLIVIN S/N SAN JACINTON° S/N DISTRITO NEPEAA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-9.07171004</t>
+          <t>-8.80170247</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-78.58178337</t>
+          <t>-78.55158891</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MAGDALENA NUEVA</t>
+          <t>PUESTO DE SALUD VINZOS</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AVENIDA AVENIDA ATAHUALPA CUADRA 3 S/N. S/N AVENIDA ATAHUALPA CUADRA 3 S/N. CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS VINZOS MZ. S LTE 02 VINZOS MZ. S LTE 02 SANTA SANTA ANCASH</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2688,27 +2688,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-8.97323873</t>
+          <t>-9.08572925</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-78.49818145</t>
+          <t>-78.57843058</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CHACHAPOYAS</t>
+          <t>CENTRO DE SALUD FLORIDA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AVENIDA AV. SANTA ROSA MZ D LTE 2 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>Jr. JR. MOQUEGUA Nº 200 JR. MOQUEGUA Nº 200 CHIMBOTE SANTA ANCASH</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2725,12 +2725,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2745,32 +2745,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>MACATE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-9.1323422</t>
+          <t>-8.75985743</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-78.51919552</t>
+          <t>-78.0598725</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD YUGOSLAVIA</t>
+          <t>PUESTO DE SALUD MACATE</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AVENIDA AV. SAUCES S/N NUEVO CHIMBOTE S/N AV. SAUCES S/N NUEVO CHIMBOTE NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>Jr. JR. ALFONSO UGARTE S/NN° S/N DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2787,12 +2787,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2807,27 +2807,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CACERES DEL PERU</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-8.93579691</t>
+          <t>-8.99045478</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-78.14516733</t>
+          <t>-78.64751719</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD LAMPANIN</t>
+          <t>PUESTO DE SALUD PUERTO SANTA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>OTROS CASERIO LAMPANIN DISTRITO CACERES DEL PERU PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS PUERTO SANTA MZA E LTE. 04 DISTRITO SANTA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2849,12 +2849,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30577</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2869,32 +2869,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>SAMANCO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-9.138176</t>
+          <t>-9.26245805</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-78.514395</t>
+          <t>-78.49625913</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO CHIMBOTE S.A.C.</t>
+          <t>PUESTO DE SALUD SAMANCO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>URBANIZACION EL AMAUTA A 14 FRENTE AL EX ESTADIO NUEVO CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS RICARDO PALMA S/N S/N RICARDO PALMA S/N SAMANCO SANTA ANCASH</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>33551</t>
+          <t>36300</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-9.07522172</t>
+          <t>-9.12696157</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-78.60341827</t>
+          <t>-78.51294523</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CENTRO MADICO SILVA CACERES</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO DEL ETERNO SOL</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Jr. LOS ALAMOSN° 201 URBANIZACION LA CALETA DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS PROGRAMA DE VIVIENDA HABILITACION URBANA ZONA ESTE I BARRIO 3 MANZANA D LOTE 1 DISTRITO CASMA PROVINCIA CASMA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2973,7 +2973,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-9.074195</t>
+          <t>-8.90842214</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-78.56754</t>
+          <t>-78.52751106</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SANTA ANA COSTA</t>
+          <t>PUESTO DE SALUD CASCAJAL</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>OTROS ASENTAMIENTO HUMANO SAN MIGUEL MANZANA L LOTE 2 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA AV.CASCAJAL S/NN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3035,12 +3035,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3055,32 +3055,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NEPEÑA</t>
+          <t>MACATE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-9.14530627</t>
+          <t>-8.88649428</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-78.27668369</t>
+          <t>-78.21585395</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SAN JACINTO</t>
+          <t>PUESTO DE SALUD SANTA ANA SIERRA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AVENIDA AV. SOLIVIN S/N SAN JACINTON° S/N DISTRITO NEPEAA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>Jr. JR. SANTA ANITA MZA. D LTE 1 DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3097,12 +3097,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3117,32 +3117,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>COISHCO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-8.80170247</t>
+          <t>-9.01984</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-78.55158891</t>
+          <t>-78.614525</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD VINZOS</t>
+          <t>CENTRO MEDICO COISHCO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>OTROS VINZOS MZ. S LTE 02 VINZOS MZ. S LTE 02 SANTA SANTA ANCASH</t>
+          <t>Jr. JR.ANCASH S/NN° S/N DISTRITO COISHCO PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3159,12 +3159,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CHIMBOTE</t>
+          <t>CACERES DEL PERU</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-9.08572925</t>
+          <t>-9.01526065</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-78.57843058</t>
+          <t>-78.13968884</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FLORIDA</t>
+          <t>PUESTO DE SALUD JIMBE</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Jr. JR. MOQUEGUA Nº 200 JR. MOQUEGUA Nº 200 CHIMBOTE SANTA ANCASH</t>
+          <t>OTROS MEDIAN VELASQUEZ S/N JIMBE S/N MEDIAN VELASQUEZ S/N JIMBE CACERES DEL PERU SANTA ANCASH</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3241,32 +3241,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MACATE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-8.75985743</t>
+          <t>-8.87030508</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-78.0598725</t>
+          <t>-78.26796167</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MACATE</t>
+          <t>PUESTO DE SALUD LUPAHUARI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Jr. JR. ALFONSO UGARTE S/NN° S/N DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS LUPAHUARY S/N CENTRO POBLADO DE LUPAHUARYN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3303,27 +3303,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>MORO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-8.99045478</t>
+          <t>-9.14204143</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-78.64751719</t>
+          <t>-78.14376285</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD PUERTO SANTA</t>
+          <t>PUESTO DE SALUD POCOS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OTROS PUERTO SANTA MZA E LTE. 04 DISTRITO SANTA PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
+          <t>OTROS CASERIO DE POCOS CASERIO DE POCOS MORO SANTA ANCASH</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3365,32 +3365,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SAMANCO</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-9.26245805</t>
+          <t>-9.0670144</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-78.49625913</t>
+          <t>-78.5974318</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SAMANCO</t>
+          <t>POLICLANICO DE COMPLEJIDAD CRECIENTE "VICTOR PANTA RODRIGUEZ"</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>OTROS RICARDO PALMA S/N S/N RICARDO PALMA S/N SAMANCO SANTA ANCASH</t>
+          <t>PROLONGACION PROLONGACION FRANCISCO PIZARRO Nº 444 BARRIO FISCAL Nº 5 DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3407,12 +3407,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3427,32 +3427,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>CHIMBOTE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-9.12696157</t>
+          <t>-9.12043129</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-78.51294523</t>
+          <t>-78.55816959</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO DEL ETERNO SOL</t>
+          <t>DEPARTAMENTO DE SANIDAD DE LA COMANDANCIA DE LA BASE NAVAL DE CHIMBOTE</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OTROS PROGRAMA DE VIVIENDA HABILITACION URBANA ZONA ESTE I BARRIO 3 MANZANA D LOTE 1 DISTRITO CASMA PROVINCIA CASMA DEPARTAMENTO ANCASH</t>
+          <t>AVENIDA LOS PESCADORES NUMERO S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3461,378 +3461,6 @@
         </is>
       </c>
       <c r="L49" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1665</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-8.90842214</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-78.52751106</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD CASCAJAL</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>AVENIDA AV.CASCAJAL S/NN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>21804</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>MACATE</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-8.88649428</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-78.21585395</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD SANTA ANA SIERRA</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Jr. JR. SANTA ANITA MZA. D LTE 1 DISTRITO MACATE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>9055</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>21803</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-9.01984</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-78.614525</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO COISHCO</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Jr. JR.ANCASH S/NN° S/N DISTRITO COISHCO PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>I-4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>21802</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CACERES DEL PERU</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-9.01526065</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-78.13968884</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD JIMBE</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>OTROS MEDIAN VELASQUEZ S/N JIMBE S/N MEDIAN VELASQUEZ S/N JIMBE CACERES DEL PERU SANTA ANCASH</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-8.87030508</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-78.26796167</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD LUPAHUARI</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>OTROS LUPAHUARY S/N CENTRO POBLADO DE LUPAHUARYN° S/N DISTRITO CHIMBOTE PROVINCIA SANTA DEPARTAMENTO ANCASH</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>021801</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21805</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>MORO</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-9.14204143</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-78.14376285</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD POCOS</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>OTROS CASERIO DE POCOS CASERIO DE POCOS MORO SANTA ANCASH</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
         <is>
           <t>021801</t>
         </is>

--- a/EstablecimientoSalud/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/EstablecimientoSalud/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-9.06854793</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>1710</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>21802</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CACERES DEL PERU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.97890945</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>1714</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>21806</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NEPEÑA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-9.17195511</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>1679</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.96477294</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>27134</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-9.057738</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>1654</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-9.08843009</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>1658</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.94403612</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>1672</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21802</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CACERES DEL PERU</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.87063242</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>27144</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-9.147672</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>1676</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21808</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.98607928</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>31454</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-9.05707165</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>1653</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-9.09278314</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>1706</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-9.1189991</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>1718</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21805</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MORO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-9.10062144</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>1675</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21803</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-9.02166397</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>17690</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-9.0746192</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>36302</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21808</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-8.993822</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>1661</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-9.05027294</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>9054</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-9.124726</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>1712</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21807</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SAMANCO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-9.31965602</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>7266</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-9.11697211</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>1660</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-9.05013822</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>1707</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-9.10852269</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>1663</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-9.05971975</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>1705</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-9.11610303</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>1713</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21807</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SAMANCO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-9.25819043</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>1674</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21804</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MACATE</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-8.76132536</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>1678</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-8.89325253</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>1669</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-9.07171004</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>1657</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-8.97323873</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>1704</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-9.1323422</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>1709</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21802</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>CACERES DEL PERU</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-8.93579691</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>36307</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-9.074195</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21806</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>NEPEÑA</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-9.14530627</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>1680</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-8.80170247</t>
@@ -2652,40 +2477,35 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>1655</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-9.08572925</t>
@@ -2714,40 +2534,35 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>1673</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21804</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>MACATE</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-8.75985743</t>
@@ -2776,40 +2591,35 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>1677</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21808</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-8.99045478</t>
@@ -2838,40 +2648,35 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>1711</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21807</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>SAMANCO</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-9.26245805</t>
@@ -2900,40 +2705,35 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>36300</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>NUEVO CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-9.12696157</t>
@@ -2962,40 +2762,35 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>1665</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-8.90842214</t>
@@ -3024,40 +2819,35 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>1668</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21804</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>MACATE</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-8.88649428</t>
@@ -3086,40 +2876,35 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>9055</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>21803</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>COISHCO</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-9.01984</t>
@@ -3148,40 +2933,35 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21802</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>CACERES DEL PERU</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-9.01526065</t>
@@ -3210,40 +2990,35 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>1667</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-8.87030508</t>
@@ -3272,40 +3047,35 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>1717</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21805</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>MORO</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-9.14204143</t>
@@ -3334,40 +3104,35 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>10013</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-9.0670144</t>
@@ -3396,40 +3161,35 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>021801</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SANTA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CHIMBOTE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>25991</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>21801</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SANTA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>CHIMBOTE</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-9.12043129</t>
@@ -3458,11 +3218,6 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>021801</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/ANCASH-SANTA-CHIMBOTE.xlsx
+++ b/EstablecimientoSalud/excels/ANCASH-SANTA-CHIMBOTE.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
